--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-moped-ext-Neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-moped-ext-Neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T06:07:01+00:00</t>
+    <t>2024-10-25T08:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
